--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.94362316959615</v>
+        <v>1.778338765059374</v>
       </c>
       <c r="D2" t="n">
-        <v>10.68184878592755</v>
+        <v>1.735800427713228</v>
       </c>
       <c r="E2" t="n">
-        <v>15.52730075512083</v>
+        <v>2.523186372707135</v>
       </c>
       <c r="F2" t="n">
-        <v>15.69625642169987</v>
+        <v>2.550641668526229</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.52264402677709</v>
+        <v>6.259929654351277</v>
       </c>
       <c r="D3" t="n">
-        <v>38.21510783272418</v>
+        <v>6.209955022817679</v>
       </c>
       <c r="E3" t="n">
-        <v>15.52730075512083</v>
+        <v>2.523186372707135</v>
       </c>
       <c r="F3" t="n">
-        <v>15.69625642169987</v>
+        <v>2.550641668526229</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.16196711028074</v>
+        <v>8.313819655420621</v>
       </c>
       <c r="D4" t="n">
-        <v>51.61679535520368</v>
+        <v>8.387729245220598</v>
       </c>
       <c r="E4" t="n">
-        <v>15.52730075512083</v>
+        <v>2.523186372707135</v>
       </c>
       <c r="F4" t="n">
-        <v>15.69625642169987</v>
+        <v>2.550641668526229</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.32512049413937</v>
+        <v>10.12783208029765</v>
       </c>
       <c r="D5" t="n">
-        <v>62.77524916578609</v>
+        <v>10.20097798944024</v>
       </c>
       <c r="E5" t="n">
-        <v>15.52730075512083</v>
+        <v>2.523186372707135</v>
       </c>
       <c r="F5" t="n">
-        <v>15.69625642169987</v>
+        <v>2.550641668526229</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.16761353769833</v>
+        <v>5.227237199875979</v>
       </c>
       <c r="D6" t="n">
-        <v>31.92915561200688</v>
+        <v>5.188487786951118</v>
       </c>
       <c r="E6" t="n">
-        <v>15.52730075512083</v>
+        <v>2.523186372707135</v>
       </c>
       <c r="F6" t="n">
-        <v>15.69625642169987</v>
+        <v>2.550641668526229</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.9238621840045</v>
+        <v>7.462627604900732</v>
       </c>
       <c r="D7" t="n">
-        <v>45.79910883862745</v>
+        <v>7.44235518627696</v>
       </c>
       <c r="E7" t="n">
-        <v>15.52730075512083</v>
+        <v>2.523186372707135</v>
       </c>
       <c r="F7" t="n">
-        <v>15.69625642169987</v>
+        <v>2.550641668526229</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.00432645239925</v>
+        <v>4.713203048514877</v>
       </c>
       <c r="D8" t="n">
-        <v>28.92095281975636</v>
+        <v>4.699654833210408</v>
       </c>
       <c r="E8" t="n">
-        <v>15.52730075512083</v>
+        <v>2.523186372707135</v>
       </c>
       <c r="F8" t="n">
-        <v>15.69625642169987</v>
+        <v>2.550641668526229</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.46963043956038</v>
+        <v>3.488814946428561</v>
       </c>
       <c r="D9" t="n">
-        <v>21.74331828263137</v>
+        <v>3.533289220927598</v>
       </c>
       <c r="E9" t="n">
-        <v>15.52730075512083</v>
+        <v>2.523186372707135</v>
       </c>
       <c r="F9" t="n">
-        <v>15.69625642169987</v>
+        <v>2.550641668526229</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
